--- a/RStudio_project/data/results_all.xlsx
+++ b/RStudio_project/data/results_all.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-6.874907164432451</v>
+        <v>-1.972636167693314</v>
       </c>
       <c r="C2" t="n">
         <v>1.670103092783505</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.159161667931221</v>
+        <v>-1.049283632293984</v>
       </c>
       <c r="E2" t="n">
-        <v>1.275351749645093</v>
+        <v>1.804946353394139</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-6.735183009183685</v>
+        <v>-1.956199091591907</v>
       </c>
       <c r="C3" t="n">
         <v>3.946587537091988</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.349642094339875</v>
+        <v>-1.068980614487171</v>
       </c>
       <c r="E3" t="n">
-        <v>3.040953765097174</v>
+        <v>3.452343409281427</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-11.53339218907319</v>
+        <v>-3.242679775137725</v>
       </c>
       <c r="C4" t="n">
         <v>3.625192012288787</v>
       </c>
       <c r="D4" t="n">
-        <v>-5.434564389199079</v>
+        <v>-1.175289337393517</v>
       </c>
       <c r="E4" t="n">
-        <v>4.058155402814538</v>
+        <v>4.445736782711019</v>
       </c>
     </row>
     <row r="5">
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-8.011310850842136</v>
+        <v>-2.174535438499942</v>
       </c>
       <c r="C5" t="n">
         <v>1.224489795918367</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.997147859128227</v>
+        <v>-0.9351442997409136</v>
       </c>
       <c r="E5" t="n">
         <v>1.109086527314828</v>
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-12.94703100188545</v>
+        <v>-3.227412570841055</v>
       </c>
       <c r="C6" t="n">
         <v>5.095796396911639</v>
       </c>
       <c r="D6" t="n">
-        <v>-15.47584121240767</v>
+        <v>-2.124491676994036</v>
       </c>
       <c r="E6" t="n">
-        <v>4.736775116704194</v>
+        <v>5.819458338063797</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-10.50850801199521</v>
+        <v>-2.594685547779418</v>
       </c>
       <c r="C7" t="n">
         <v>2.743022136669875</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.215461076147316</v>
+        <v>-0.9403661085080375</v>
       </c>
       <c r="E7" t="n">
-        <v>2.022103312818705</v>
+        <v>2.559036545772476</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-7.602682124543102</v>
+        <v>-2.062021415167948</v>
       </c>
       <c r="C8" t="n">
         <v>1.015572105619499</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.276751712120006</v>
+        <v>-0.9403616703890749</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8008526885594991</v>
+        <v>0.9618832843727034</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-9.216217679619115</v>
+        <v>-2.28203825723654</v>
       </c>
       <c r="C9" t="n">
         <v>3.790781978249612</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.38594782056169</v>
+        <v>-1.095634761122136</v>
       </c>
       <c r="E9" t="n">
-        <v>3.430441147907665</v>
+        <v>3.924779927279411</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-8.47705488858835</v>
+        <v>-2.166294740019482</v>
       </c>
       <c r="C10" t="n">
         <v>1.893048128342246</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.691232871211211</v>
+        <v>-0.8954621316629091</v>
       </c>
       <c r="E10" t="n">
-        <v>1.888555526241195</v>
+        <v>2.456543224986303</v>
       </c>
     </row>
     <row r="11">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-9.464665147158108</v>
+        <v>-2.324524965043218</v>
       </c>
       <c r="C11" t="n">
         <v>4.101876675603217</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.167191216619933</v>
+        <v>-1.086301620329818</v>
       </c>
       <c r="E11" t="n">
-        <v>3.932309629264858</v>
+        <v>4.360159776163091</v>
       </c>
     </row>
   </sheetData>

--- a/RStudio_project/data/results_all.xlsx
+++ b/RStudio_project/data/results_all.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.972636167693314</v>
+        <v>-2.108381897440729</v>
       </c>
       <c r="C2" t="n">
-        <v>1.670103092783505</v>
+        <v>3.298969072164948</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.049283632293984</v>
+        <v>-1.885978918357454</v>
       </c>
       <c r="E2" t="n">
-        <v>1.804946353394139</v>
+        <v>3.606448108298784</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.956199091591907</v>
+        <v>-2.454168279098111</v>
       </c>
       <c r="C3" t="n">
-        <v>3.946587537091988</v>
+        <v>4.836795252225519</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.068980614487171</v>
+        <v>-3.066837168189372</v>
       </c>
       <c r="E3" t="n">
-        <v>3.452343409281427</v>
+        <v>4.456060380982636</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-3.242679775137725</v>
+        <v>-3.781589951673457</v>
       </c>
       <c r="C4" t="n">
-        <v>3.625192012288787</v>
+        <v>4.608294930875577</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.175289337393517</v>
+        <v>-3.98593227447337</v>
       </c>
       <c r="E4" t="n">
-        <v>4.445736782711019</v>
+        <v>5.254724851429905</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.174535438499942</v>
+        <v>-2.674618878699453</v>
       </c>
       <c r="C5" t="n">
-        <v>1.224489795918367</v>
+        <v>1.63265306122449</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9351442997409136</v>
+        <v>-1.565407532602706</v>
       </c>
       <c r="E5" t="n">
-        <v>1.109086527314828</v>
+        <v>1.638561917646507</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.227412570841055</v>
+        <v>-3.856549013631771</v>
       </c>
       <c r="C6" t="n">
-        <v>5.095796396911639</v>
+        <v>6.502716614240778</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.124491676994036</v>
+        <v>-8.874911227309752</v>
       </c>
       <c r="E6" t="n">
-        <v>5.819458338063797</v>
+        <v>7.158463897064413</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-2.594685547779418</v>
+        <v>-3.063880232553046</v>
       </c>
       <c r="C7" t="n">
-        <v>2.743022136669875</v>
+        <v>3.43599615014437</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9403661085080375</v>
+        <v>-1.67088202018397</v>
       </c>
       <c r="E7" t="n">
-        <v>2.559036545772476</v>
+        <v>3.252055134086865</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2.062021415167948</v>
+        <v>-2.568563805312492</v>
       </c>
       <c r="C8" t="n">
-        <v>1.015572105619499</v>
+        <v>1.462423832092079</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9403616703890749</v>
+        <v>-1.754167991606151</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9618832843727034</v>
+        <v>1.42681648871446</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-2.28203825723654</v>
+        <v>-2.872345369714373</v>
       </c>
       <c r="C9" t="n">
-        <v>3.790781978249612</v>
+        <v>4.536509580528224</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.095634761122136</v>
+        <v>-4.8216793442989</v>
       </c>
       <c r="E9" t="n">
-        <v>3.924779927279411</v>
+        <v>4.333151232966168</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.166294740019482</v>
+        <v>-2.625413978895157</v>
       </c>
       <c r="C10" t="n">
-        <v>1.893048128342246</v>
+        <v>3.080213903743315</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8954621316629091</v>
+        <v>-1.556071850085122</v>
       </c>
       <c r="E10" t="n">
-        <v>2.456543224986303</v>
+        <v>3.075311568574241</v>
       </c>
     </row>
     <row r="11">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-2.324524965043218</v>
+        <v>-2.871952565297041</v>
       </c>
       <c r="C11" t="n">
-        <v>4.101876675603217</v>
+        <v>4.664879356568364</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.086301620329818</v>
+        <v>-4.266184761036848</v>
       </c>
       <c r="E11" t="n">
-        <v>4.360159776163091</v>
+        <v>4.990489242064369</v>
       </c>
     </row>
   </sheetData>

--- a/RStudio_project/data/results_all.xlsx
+++ b/RStudio_project/data/results_all.xlsx
@@ -462,13 +462,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.108381897440729</v>
+        <v>-2.4074289275815</v>
       </c>
       <c r="C2" t="n">
         <v>3.298969072164948</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.885978918357454</v>
+        <v>-1.590033183065876</v>
       </c>
       <c r="E2" t="n">
         <v>3.606448108298784</v>
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2.454168279098111</v>
+        <v>-2.604982896780644</v>
       </c>
       <c r="C3" t="n">
         <v>4.836795252225519</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.066837168189372</v>
+        <v>-1.599475751465367</v>
       </c>
       <c r="E3" t="n">
         <v>4.456060380982636</v>
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-3.781589951673457</v>
+        <v>-3.752113555133737</v>
       </c>
       <c r="C4" t="n">
         <v>4.608294930875577</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.98593227447337</v>
+        <v>-1.663035901660481</v>
       </c>
       <c r="E4" t="n">
         <v>5.254724851429905</v>
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.674618878699453</v>
+        <v>-2.643519487635751</v>
       </c>
       <c r="C5" t="n">
         <v>1.63265306122449</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.565407532602706</v>
+        <v>-1.254216534740712</v>
       </c>
       <c r="E5" t="n">
         <v>1.638561917646507</v>
@@ -538,13 +538,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.856549013631771</v>
+        <v>-3.823349866722797</v>
       </c>
       <c r="C6" t="n">
         <v>6.502716614240778</v>
       </c>
       <c r="D6" t="n">
-        <v>-8.874911227309752</v>
+        <v>-2.666418900030991</v>
       </c>
       <c r="E6" t="n">
         <v>7.158463897064413</v>
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-3.063880232553046</v>
+        <v>-3.111388064848645</v>
       </c>
       <c r="C7" t="n">
         <v>3.43599615014437</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.67088202018397</v>
+        <v>-1.404136937499034</v>
       </c>
       <c r="E7" t="n">
         <v>3.252055134086865</v>
@@ -576,13 +576,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2.568563805312492</v>
+        <v>-2.585120619136991</v>
       </c>
       <c r="C8" t="n">
         <v>1.462423832092079</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.754167991606151</v>
+        <v>-1.366906866610701</v>
       </c>
       <c r="E8" t="n">
         <v>1.42681648871446</v>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-2.872345369714373</v>
+        <v>-2.854574221177639</v>
       </c>
       <c r="C9" t="n">
         <v>4.536509580528224</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8216793442989</v>
+        <v>-1.648583639561908</v>
       </c>
       <c r="E9" t="n">
         <v>4.333151232966168</v>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.625413978895157</v>
+        <v>-2.734136570730855</v>
       </c>
       <c r="C10" t="n">
         <v>3.080213903743315</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.556071850085122</v>
+        <v>-1.351779791590276</v>
       </c>
       <c r="E10" t="n">
         <v>3.075311568574241</v>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-2.871952565297041</v>
+        <v>-2.81723120132831</v>
       </c>
       <c r="C11" t="n">
         <v>4.664879356568364</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.266184761036848</v>
+        <v>-1.654470506057926</v>
       </c>
       <c r="E11" t="n">
         <v>4.990489242064369</v>
